--- a/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
+++ b/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C29" s="16" t="n"/>

--- a/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
+++ b/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="C29" s="16" t="n"/>

--- a/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
+++ b/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="C29" s="16" t="n"/>

--- a/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
+++ b/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="C29" s="16" t="n"/>

--- a/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
+++ b/projects/nano-nico-recruitment/recruitment_outputs/nico_recruitment_milestones_latest.xlsx
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C29" s="16" t="n"/>
